--- a/samples/new_phase1_260109R_data.xlsx
+++ b/samples/new_phase1_260109R_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew Liu\Report Generator\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEC545F-C706-457A-A816-A0086C0C55FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDC6535-C18D-4F4C-854A-1BE372639A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="104">
   <si>
     <t>client_name</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Caltex</t>
+  </si>
+  <si>
+    <t>Based on the findings of this Phase I ESA, a Phase II Environmental Site Assessment is NOT recommended to further evaluate identified areas of potential environmental concern.</t>
   </si>
 </sst>
 </file>
@@ -675,13 +678,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -907,7 +910,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1017,10 +1020,10 @@
         <v>64</v>
       </c>
       <c r="AK3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -1367,9 +1370,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1405,9 +1408,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1443,9 +1446,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>80</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1467,7 +1470,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1489,7 +1492,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1500,7 +1503,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1511,7 +1514,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
